--- a/Outputs/Scenarios/PtX_demand_EE_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_EE_Electrification.xlsx
@@ -803,7 +803,7 @@
         <v>0.001636165311418535</v>
       </c>
       <c r="G10" t="n">
-        <v>5.882606390480593e-06</v>
+        <v>5.882606390480594e-06</v>
       </c>
       <c r="H10" t="n">
         <v>0.0003132736250605999</v>
@@ -840,7 +840,7 @@
         <v>0.01617614087513679</v>
       </c>
       <c r="G11" t="n">
-        <v>4.142947176255379e-05</v>
+        <v>4.14294717625538e-05</v>
       </c>
       <c r="H11" t="n">
         <v>0.002863152017891</v>
@@ -1555,7 +1555,7 @@
         <v>0.0005174428610021083</v>
       </c>
       <c r="K30" t="n">
-        <v>0.007597790837806659</v>
+        <v>0.007597790837806658</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.005065193891871107</v>
+        <v>0.005065193891871106</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.007597790837806659</v>
+        <v>0.007597790837806658</v>
       </c>
     </row>
     <row r="34">

--- a/Outputs/Scenarios/PtX_demand_EE_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_EE_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0003495342219082036</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001290459603866285</v>
+        <v>0.001373432080341904</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0002150766006443809</v>
+        <v>0.0002849629009483629</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0008603064025775235</v>
+        <v>0.001139851603793452</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001290459603866285</v>
+        <v>0.001139851603793452</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>2.801173772863643e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.001786212120719948</v>
+        <v>0.001753627052544788</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.000169555107403047</v>
       </c>
       <c r="K25" t="n">
-        <v>0.01749191688714779</v>
+        <v>0.01717281967709627</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>5.036196475490044e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0002150766006443809</v>
+        <v>0.0002849629009483629</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.0005174428610021083</v>
       </c>
       <c r="K30" t="n">
-        <v>0.007597790837806658</v>
+        <v>0.007412904611902663</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.001266298472967777</v>
+        <v>0.001538046790151732</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.005065193891871106</v>
+        <v>0.006152187160606928</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.007597790837806658</v>
+        <v>0.006152187160606928</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>2.723383478958465e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.001266298472967777</v>
+        <v>0.001538046790151732</v>
       </c>
     </row>
     <row r="43">
